--- a/Tools/Luban/DataTables/Datas/多语言_Language.xlsx
+++ b/Tools/Luban/DataTables/Datas/多语言_Language.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="321">
   <si>
     <t>##var</t>
   </si>
@@ -43,6 +43,12 @@
     <t/>
   </si>
   <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>×</t>
+  </si>
+  <si>
     <t>season_spring</t>
   </si>
   <si>
@@ -935,6 +941,42 @@
   </si>
   <si>
     <t>结束</t>
+  </si>
+  <si>
+    <t>tab_all</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>tab_material</t>
+  </si>
+  <si>
+    <t>材料</t>
+  </si>
+  <si>
+    <t>tab_seed</t>
+  </si>
+  <si>
+    <t>种子</t>
+  </si>
+  <si>
+    <t>tab_product</t>
+  </si>
+  <si>
+    <t>产品</t>
+  </si>
+  <si>
+    <t>btn_use</t>
+  </si>
+  <si>
+    <t>使用</t>
+  </si>
+  <si>
+    <t>btn_discard</t>
+  </si>
+  <si>
+    <t>丢弃</t>
   </si>
 </sst>
 </file>
@@ -947,7 +989,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -958,13 +1000,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1444,148 +1479,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1943,7 +1978,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C162"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2487,7 +2522,7 @@
         <v>99</v>
       </c>
       <c r="C49" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -2495,7 +2530,7 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C50" t="s">
         <v>88</v>
@@ -2506,10 +2541,10 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -2531,7 +2566,7 @@
         <v>105</v>
       </c>
       <c r="C53" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -2539,7 +2574,7 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C54" t="s">
         <v>96</v>
@@ -2550,10 +2585,10 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C55" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -2608,7 +2643,7 @@
         <v>117</v>
       </c>
       <c r="C60" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -2616,10 +2651,10 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C61" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2927,7 +2962,7 @@
         <v>174</v>
       </c>
       <c r="C89" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2935,10 +2970,10 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C90" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -3158,7 +3193,7 @@
         <v>215</v>
       </c>
       <c r="C110" t="s">
-        <v>145</v>
+        <v>216</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -3166,10 +3201,10 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C111" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -3177,10 +3212,10 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C112" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -3188,10 +3223,10 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C113" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -3199,10 +3234,10 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C114" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -3210,10 +3245,10 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C115" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -3345,7 +3380,7 @@
         <v>244</v>
       </c>
       <c r="C127" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -3353,10 +3388,10 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C128" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -3364,10 +3399,10 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C129" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -3375,10 +3410,10 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C130" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -3386,10 +3421,10 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C131" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -3397,10 +3432,10 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C132" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -3408,10 +3443,10 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C133" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -3419,10 +3454,10 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C134" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -3430,10 +3465,10 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C135" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -3441,10 +3476,10 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C136" t="s">
-        <v>254</v>
+        <v>210</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -3722,12 +3757,71 @@
         <v>304</v>
       </c>
     </row>
-    <row r="162" spans="2:3">
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
+        <v>8</v>
+      </c>
       <c r="B162" t="s">
         <v>305</v>
       </c>
       <c r="C162" t="s">
         <v>306</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3">
+      <c r="B163" t="s">
+        <v>307</v>
+      </c>
+      <c r="C163" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3">
+      <c r="B164" t="s">
+        <v>309</v>
+      </c>
+      <c r="C164" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3">
+      <c r="B165" t="s">
+        <v>311</v>
+      </c>
+      <c r="C165" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3">
+      <c r="B166" t="s">
+        <v>313</v>
+      </c>
+      <c r="C166" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3">
+      <c r="B167" t="s">
+        <v>315</v>
+      </c>
+      <c r="C167" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3">
+      <c r="B168" t="s">
+        <v>317</v>
+      </c>
+      <c r="C168" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3">
+      <c r="B169" t="s">
+        <v>319</v>
+      </c>
+      <c r="C169" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
